--- a/Uitwerkingen/Week6/reportRetail.xlsx
+++ b/Uitwerkingen/Week6/reportRetail.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Percentage that category contributes to total sales</t>
+          <t>Percentage that category contributes to total sales (%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Percentage of total sales</t>
+          <t>Percentage of total sales (%)</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Feburary</t>
+          <t>February</t>
         </is>
       </c>
       <c r="F3" t="n">
